--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -837,7 +837,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -887,7 +887,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -937,7 +937,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -1137,7 +1137,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -1237,7 +1237,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>

--- a/Planning/MASTER_TASK_LIST.xlsx
+++ b/Planning/MASTER_TASK_LIST.xlsx
@@ -1287,12 +1287,16 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NOT_STARTED</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Tranche A (order state machine, customer cancel, tracking fields, return-request create/list) implemented and committed (5af12bd); COM-004 security review finding F-1 (duplicate variantId quantity-invariant bypass) remediated and independently re-verified PASS (43d1af1). Tranche B (staff/admin order management, payment/refund integration, inventory decrement, return-window enforcement, return approve/reject/receive) remains NOT_STARTED and is required before this task is COMPLETED.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
